--- a/data/roles.xlsx
+++ b/data/roles.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>view_tasks,complete_tasks,edit_equipment,manage_users,manage_roles</t>
+          <t>view_dashboard,manage_schedule,complete_tasks,manage_settings,manage_users,view_tasks,edit_equipment,manage_roles</t>
         </is>
       </c>
     </row>
